--- a/inputs/bess_installs_capex.xlsx
+++ b/inputs/bess_installs_capex.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9c6ffa232d49179/Documents/Solar_BESS/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barna\PycharmProjects\solar_bess\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{2B54CD34-4F41-4A71-BD30-FFDF0095B63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE3343BE-7A40-434C-8F0B-7286608AF0BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58918E2C-AE97-4EAA-82AA-01F6EE5C5DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B92BE577-E5A6-49BC-BFF6-C9C17C524DC8}"/>
+    <workbookView xWindow="17550" yWindow="-13995" windowWidth="20760" windowHeight="12390" xr2:uid="{B92BE577-E5A6-49BC-BFF6-C9C17C524DC8}"/>
   </bookViews>
   <sheets>
     <sheet name="battery_kwh" sheetId="2" r:id="rId1"/>

--- a/inputs/bess_installs_capex.xlsx
+++ b/inputs/bess_installs_capex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barna\PycharmProjects\solar_bess\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58918E2C-AE97-4EAA-82AA-01F6EE5C5DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9DB3F9-E39B-41A9-A457-F03FD87E782B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17550" yWindow="-13995" windowWidth="20760" windowHeight="12390" xr2:uid="{B92BE577-E5A6-49BC-BFF6-C9C17C524DC8}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19360" windowHeight="11440" xr2:uid="{B92BE577-E5A6-49BC-BFF6-C9C17C524DC8}"/>
   </bookViews>
   <sheets>
     <sheet name="battery_kwh" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>Year</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>$/kWh</t>
+  </si>
+  <si>
+    <t>Bloomberg (2024 $/kWh)</t>
   </si>
 </sst>
 </file>
@@ -3134,7 +3137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77809882-715C-4DF3-8312-C700D0A8AD40}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.81640625" customWidth="1"/>
@@ -3144,7 +3147,7 @@
     <col min="10" max="10" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B1" s="16" t="s">
         <v>9</v>
       </c>
@@ -3165,7 +3168,7 @@
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
     </row>
-    <row r="2" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3206,8 +3209,11 @@
       <c r="O2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="R2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2010</v>
       </c>
@@ -3232,7 +3238,7 @@
         <v>1.5499999999999999E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2011</v>
       </c>
@@ -3257,7 +3263,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2012</v>
       </c>
@@ -3282,7 +3288,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2013</v>
       </c>
@@ -3321,7 +3327,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2014</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>2015</v>
       </c>
@@ -3399,7 +3405,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>2016</v>
       </c>
@@ -3437,8 +3443,14 @@
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q9">
+        <v>2017</v>
+      </c>
+      <c r="R9" s="14">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>2017</v>
       </c>
@@ -3482,8 +3494,14 @@
         <f t="shared" si="0"/>
         <v>0.06</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q10">
+        <v>2018</v>
+      </c>
+      <c r="R10" s="14">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>2018</v>
       </c>
@@ -3527,8 +3545,14 @@
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q11">
+        <v>2019</v>
+      </c>
+      <c r="R11" s="14">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>2019</v>
       </c>
@@ -3572,8 +3596,14 @@
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q12">
+        <v>2020</v>
+      </c>
+      <c r="R12" s="14">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>2020</v>
       </c>
@@ -3617,8 +3647,14 @@
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q13">
+        <v>2021</v>
+      </c>
+      <c r="R13" s="14">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>2021</v>
       </c>
@@ -3662,8 +3698,14 @@
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q14">
+        <v>2022</v>
+      </c>
+      <c r="R14" s="14">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>2022</v>
       </c>
@@ -3707,8 +3749,14 @@
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q15">
+        <v>2023</v>
+      </c>
+      <c r="R15" s="14">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>2023</v>
       </c>
@@ -3752,8 +3800,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q16">
+        <v>2024</v>
+      </c>
+      <c r="R16" s="14">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>2024</v>
       </c>
@@ -3797,8 +3851,14 @@
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q17">
+        <v>2025</v>
+      </c>
+      <c r="R17" s="14">
+        <v>113.9240506329114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L18">
         <v>2007</v>
       </c>
@@ -3813,7 +3873,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L19">
         <v>2008</v>
       </c>
@@ -3828,7 +3888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L20">
         <v>2009</v>
       </c>
@@ -3843,7 +3903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L21">
         <v>2010</v>
       </c>
@@ -3858,7 +3918,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L22">
         <v>2011</v>
       </c>
@@ -3873,7 +3933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L23">
         <v>2012</v>
       </c>
@@ -3888,7 +3948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L24">
         <v>2013</v>
       </c>
@@ -3903,7 +3963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L25">
         <v>2014</v>
       </c>
@@ -3918,7 +3978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L26">
         <v>2015</v>
       </c>
@@ -3933,7 +3993,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="L27">
         <v>2016</v>
       </c>
